--- a/StructureDefinition-research-study-associated-party.xlsx
+++ b/StructureDefinition-research-study-associated-party.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-26T23:53:55+00:00</t>
+    <t>2025-12-03T18:37:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1273,7 +1273,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" hidden="true">
+    <row r="5">
       <c r="A5" t="s" s="2">
         <v>95</v>
       </c>
@@ -1792,7 +1792,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
         <v>117</v>
       </c>
@@ -3345,7 +3345,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
         <v>143</v>
       </c>
@@ -4074,12 +4074,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AK31">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/StructureDefinition-research-study-associated-party.xlsx
+++ b/StructureDefinition-research-study-associated-party.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-03T18:37:31+00:00</t>
+    <t>2025-12-03T22:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>NCPI FHIR Working Group (http://example.org/example-publisher, ncpi-fhir-ig@googlegroups.com)</t>
+    <t>NCPI FHIR Working Group (https://www.ncpi-acc.org/about/working-groups, ncpi-fhir-ig@googlegroups.com)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/StructureDefinition-research-study-associated-party.xlsx
+++ b/StructureDefinition-research-study-associated-party.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-03T22:26:51+00:00</t>
+    <t>2026-01-13T18:03:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-research-study-associated-party.xlsx
+++ b/StructureDefinition-research-study-associated-party.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-13T18:03:13+00:00</t>
+    <t>2026-02-06T18:07:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-research-study-associated-party.xlsx
+++ b/StructureDefinition-research-study-associated-party.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-06T18:07:39+00:00</t>
+    <t>2026-03-09T20:11:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
